--- a/docs/intake-template.xlsx
+++ b/docs/intake-template.xlsx
@@ -16,11 +16,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기본정보'!$A$1:$C$301</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'품목'!$A$1:$M$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'품목'!$A$1:$O$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'제품유형'!$A$1:$B$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'표시사항'!$A$1:$D$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'제조공정'!$A$1:$C$301</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'성분'!$A$1:$H$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'성분'!$A$1:$K$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2143,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:O301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2159,8 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2227,6 +2229,16 @@
           <t>출처</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>제조일자</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>대표품목</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -2242,6 +2254,8 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -2257,6 +2271,8 @@
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -2272,6 +2288,8 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -2287,6 +2305,8 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -2302,6 +2322,8 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -2317,6 +2339,8 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -2332,6 +2356,8 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -2347,6 +2373,8 @@
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -2362,6 +2390,8 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -2377,6 +2407,8 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -2392,6 +2424,8 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -2407,6 +2441,8 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -2422,6 +2458,8 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -2437,6 +2475,8 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -2452,6 +2492,8 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -2467,6 +2509,8 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -2482,6 +2526,8 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2497,6 +2543,8 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2512,6 +2560,8 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2527,6 +2577,8 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2542,6 +2594,8 @@
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2557,6 +2611,8 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2572,6 +2628,8 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2587,6 +2645,8 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2602,6 +2662,8 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2617,6 +2679,8 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2632,6 +2696,8 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2647,6 +2713,8 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2662,6 +2730,8 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2677,6 +2747,8 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2692,6 +2764,8 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2707,6 +2781,8 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2722,6 +2798,8 @@
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2737,6 +2815,8 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2752,6 +2832,8 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2767,6 +2849,8 @@
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2782,6 +2866,8 @@
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2797,6 +2883,8 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2812,6 +2900,8 @@
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2827,6 +2917,8 @@
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2842,6 +2934,8 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2857,6 +2951,8 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2872,6 +2968,8 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2887,6 +2985,8 @@
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2902,6 +3002,8 @@
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2917,6 +3019,8 @@
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2932,6 +3036,8 @@
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -2947,6 +3053,8 @@
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2962,6 +3070,8 @@
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -2977,6 +3087,8 @@
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2992,6 +3104,8 @@
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3007,6 +3121,8 @@
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3022,6 +3138,8 @@
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3037,6 +3155,8 @@
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3052,6 +3172,8 @@
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3067,6 +3189,8 @@
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3082,6 +3206,8 @@
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3097,6 +3223,8 @@
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3112,6 +3240,8 @@
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -3127,6 +3257,8 @@
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -3142,6 +3274,8 @@
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -3157,6 +3291,8 @@
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -3172,6 +3308,8 @@
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -3187,6 +3325,8 @@
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -3202,6 +3342,8 @@
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -3217,6 +3359,8 @@
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -3232,6 +3376,8 @@
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -3247,6 +3393,8 @@
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -3262,6 +3410,8 @@
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -3277,6 +3427,8 @@
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -3292,6 +3444,8 @@
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -3307,6 +3461,8 @@
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -3322,6 +3478,8 @@
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -3337,6 +3495,8 @@
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -3352,6 +3512,8 @@
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -3367,6 +3529,8 @@
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n"/>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -3382,6 +3546,8 @@
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -3397,6 +3563,8 @@
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -3412,6 +3580,8 @@
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -3427,6 +3597,8 @@
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -3442,6 +3614,8 @@
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -3457,6 +3631,8 @@
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -3472,6 +3648,8 @@
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -3487,6 +3665,8 @@
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n"/>
+      <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -3502,6 +3682,8 @@
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -3517,6 +3699,8 @@
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n"/>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -3532,6 +3716,8 @@
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -3547,6 +3733,8 @@
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -3562,6 +3750,8 @@
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="2" t="n"/>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -3577,6 +3767,8 @@
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="2" t="n"/>
+      <c r="N91" s="2" t="n"/>
+      <c r="O91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -3592,6 +3784,8 @@
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -3607,6 +3801,8 @@
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -3622,6 +3818,8 @@
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -3637,6 +3835,8 @@
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
+      <c r="N95" s="2" t="n"/>
+      <c r="O95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -3652,6 +3852,8 @@
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -3667,6 +3869,8 @@
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
+      <c r="O97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -3682,6 +3886,8 @@
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -3697,6 +3903,8 @@
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="2" t="n"/>
+      <c r="N99" s="2" t="n"/>
+      <c r="O99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -3712,6 +3920,8 @@
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -3727,6 +3937,8 @@
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="2" t="n"/>
+      <c r="N101" s="2" t="n"/>
+      <c r="O101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -3742,6 +3954,8 @@
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -3757,6 +3971,8 @@
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -3772,6 +3988,8 @@
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -3787,6 +4005,8 @@
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -3802,6 +4022,8 @@
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -3817,6 +4039,8 @@
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -3832,6 +4056,8 @@
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
+      <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -3847,6 +4073,8 @@
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="n"/>
+      <c r="O109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -3862,6 +4090,8 @@
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -3877,6 +4107,8 @@
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
+      <c r="N111" s="2" t="n"/>
+      <c r="O111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -3892,6 +4124,8 @@
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -3907,6 +4141,8 @@
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -3922,6 +4158,8 @@
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -3937,6 +4175,8 @@
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="2" t="n"/>
+      <c r="N115" s="2" t="n"/>
+      <c r="O115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -3952,6 +4192,8 @@
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="n"/>
       <c r="M116" s="2" t="n"/>
+      <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -3967,6 +4209,8 @@
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="n"/>
       <c r="M117" s="2" t="n"/>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -3982,6 +4226,8 @@
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="2" t="n"/>
+      <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -3997,6 +4243,8 @@
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -4012,6 +4260,8 @@
       <c r="K120" s="2" t="n"/>
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -4027,6 +4277,8 @@
       <c r="K121" s="2" t="n"/>
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -4042,6 +4294,8 @@
       <c r="K122" s="2" t="n"/>
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -4057,6 +4311,8 @@
       <c r="K123" s="2" t="n"/>
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
+      <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -4072,6 +4328,8 @@
       <c r="K124" s="2" t="n"/>
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -4087,6 +4345,8 @@
       <c r="K125" s="2" t="n"/>
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="2" t="n"/>
+      <c r="N125" s="2" t="n"/>
+      <c r="O125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -4102,6 +4362,8 @@
       <c r="K126" s="2" t="n"/>
       <c r="L126" s="2" t="n"/>
       <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -4117,6 +4379,8 @@
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="2" t="n"/>
+      <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -4132,6 +4396,8 @@
       <c r="K128" s="2" t="n"/>
       <c r="L128" s="2" t="n"/>
       <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -4147,6 +4413,8 @@
       <c r="K129" s="2" t="n"/>
       <c r="L129" s="2" t="n"/>
       <c r="M129" s="2" t="n"/>
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -4162,6 +4430,8 @@
       <c r="K130" s="2" t="n"/>
       <c r="L130" s="2" t="n"/>
       <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -4177,6 +4447,8 @@
       <c r="K131" s="2" t="n"/>
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -4192,6 +4464,8 @@
       <c r="K132" s="2" t="n"/>
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="2" t="n"/>
+      <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -4207,6 +4481,8 @@
       <c r="K133" s="2" t="n"/>
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="2" t="n"/>
+      <c r="N133" s="2" t="n"/>
+      <c r="O133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -4222,6 +4498,8 @@
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -4237,6 +4515,8 @@
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
+      <c r="N135" s="2" t="n"/>
+      <c r="O135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -4252,6 +4532,8 @@
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
+      <c r="N136" s="2" t="n"/>
+      <c r="O136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -4267,6 +4549,8 @@
       <c r="K137" s="2" t="n"/>
       <c r="L137" s="2" t="n"/>
       <c r="M137" s="2" t="n"/>
+      <c r="N137" s="2" t="n"/>
+      <c r="O137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -4282,6 +4566,8 @@
       <c r="K138" s="2" t="n"/>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -4297,6 +4583,8 @@
       <c r="K139" s="2" t="n"/>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
+      <c r="N139" s="2" t="n"/>
+      <c r="O139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -4312,6 +4600,8 @@
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="2" t="n"/>
+      <c r="N140" s="2" t="n"/>
+      <c r="O140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -4327,6 +4617,8 @@
       <c r="K141" s="2" t="n"/>
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="2" t="n"/>
+      <c r="N141" s="2" t="n"/>
+      <c r="O141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -4342,6 +4634,8 @@
       <c r="K142" s="2" t="n"/>
       <c r="L142" s="2" t="n"/>
       <c r="M142" s="2" t="n"/>
+      <c r="N142" s="2" t="n"/>
+      <c r="O142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -4357,6 +4651,8 @@
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
+      <c r="N143" s="2" t="n"/>
+      <c r="O143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -4372,6 +4668,8 @@
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="2" t="n"/>
+      <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -4387,6 +4685,8 @@
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="2" t="n"/>
+      <c r="N145" s="2" t="n"/>
+      <c r="O145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -4402,6 +4702,8 @@
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="2" t="n"/>
+      <c r="N146" s="2" t="n"/>
+      <c r="O146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -4417,6 +4719,8 @@
       <c r="K147" s="2" t="n"/>
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="2" t="n"/>
+      <c r="N147" s="2" t="n"/>
+      <c r="O147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -4432,6 +4736,8 @@
       <c r="K148" s="2" t="n"/>
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="2" t="n"/>
+      <c r="N148" s="2" t="n"/>
+      <c r="O148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -4447,6 +4753,8 @@
       <c r="K149" s="2" t="n"/>
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="2" t="n"/>
+      <c r="N149" s="2" t="n"/>
+      <c r="O149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -4462,6 +4770,8 @@
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
+      <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -4477,6 +4787,8 @@
       <c r="K151" s="2" t="n"/>
       <c r="L151" s="2" t="n"/>
       <c r="M151" s="2" t="n"/>
+      <c r="N151" s="2" t="n"/>
+      <c r="O151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -4492,6 +4804,8 @@
       <c r="K152" s="2" t="n"/>
       <c r="L152" s="2" t="n"/>
       <c r="M152" s="2" t="n"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -4507,6 +4821,8 @@
       <c r="K153" s="2" t="n"/>
       <c r="L153" s="2" t="n"/>
       <c r="M153" s="2" t="n"/>
+      <c r="N153" s="2" t="n"/>
+      <c r="O153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -4522,6 +4838,8 @@
       <c r="K154" s="2" t="n"/>
       <c r="L154" s="2" t="n"/>
       <c r="M154" s="2" t="n"/>
+      <c r="N154" s="2" t="n"/>
+      <c r="O154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -4537,6 +4855,8 @@
       <c r="K155" s="2" t="n"/>
       <c r="L155" s="2" t="n"/>
       <c r="M155" s="2" t="n"/>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -4552,6 +4872,8 @@
       <c r="K156" s="2" t="n"/>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
+      <c r="N156" s="2" t="n"/>
+      <c r="O156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -4567,6 +4889,8 @@
       <c r="K157" s="2" t="n"/>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
+      <c r="N157" s="2" t="n"/>
+      <c r="O157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -4582,6 +4906,8 @@
       <c r="K158" s="2" t="n"/>
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
+      <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -4597,6 +4923,8 @@
       <c r="K159" s="2" t="n"/>
       <c r="L159" s="2" t="n"/>
       <c r="M159" s="2" t="n"/>
+      <c r="N159" s="2" t="n"/>
+      <c r="O159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -4612,6 +4940,8 @@
       <c r="K160" s="2" t="n"/>
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="2" t="n"/>
+      <c r="N160" s="2" t="n"/>
+      <c r="O160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -4627,6 +4957,8 @@
       <c r="K161" s="2" t="n"/>
       <c r="L161" s="2" t="n"/>
       <c r="M161" s="2" t="n"/>
+      <c r="N161" s="2" t="n"/>
+      <c r="O161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -4642,6 +4974,8 @@
       <c r="K162" s="2" t="n"/>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="2" t="n"/>
+      <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -4657,6 +4991,8 @@
       <c r="K163" s="2" t="n"/>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="2" t="n"/>
+      <c r="N163" s="2" t="n"/>
+      <c r="O163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -4672,6 +5008,8 @@
       <c r="K164" s="2" t="n"/>
       <c r="L164" s="2" t="n"/>
       <c r="M164" s="2" t="n"/>
+      <c r="N164" s="2" t="n"/>
+      <c r="O164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -4687,6 +5025,8 @@
       <c r="K165" s="2" t="n"/>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="2" t="n"/>
+      <c r="N165" s="2" t="n"/>
+      <c r="O165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -4702,6 +5042,8 @@
       <c r="K166" s="2" t="n"/>
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="2" t="n"/>
+      <c r="N166" s="2" t="n"/>
+      <c r="O166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -4717,6 +5059,8 @@
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="2" t="n"/>
+      <c r="N167" s="2" t="n"/>
+      <c r="O167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -4732,6 +5076,8 @@
       <c r="K168" s="2" t="n"/>
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n"/>
+      <c r="N168" s="2" t="n"/>
+      <c r="O168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -4747,6 +5093,8 @@
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="2" t="n"/>
+      <c r="N169" s="2" t="n"/>
+      <c r="O169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -4762,6 +5110,8 @@
       <c r="K170" s="2" t="n"/>
       <c r="L170" s="2" t="n"/>
       <c r="M170" s="2" t="n"/>
+      <c r="N170" s="2" t="n"/>
+      <c r="O170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -4777,6 +5127,8 @@
       <c r="K171" s="2" t="n"/>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="2" t="n"/>
+      <c r="N171" s="2" t="n"/>
+      <c r="O171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -4792,6 +5144,8 @@
       <c r="K172" s="2" t="n"/>
       <c r="L172" s="2" t="n"/>
       <c r="M172" s="2" t="n"/>
+      <c r="N172" s="2" t="n"/>
+      <c r="O172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -4807,6 +5161,8 @@
       <c r="K173" s="2" t="n"/>
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="2" t="n"/>
+      <c r="N173" s="2" t="n"/>
+      <c r="O173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -4822,6 +5178,8 @@
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="2" t="n"/>
+      <c r="N174" s="2" t="n"/>
+      <c r="O174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -4837,6 +5195,8 @@
       <c r="K175" s="2" t="n"/>
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="2" t="n"/>
+      <c r="N175" s="2" t="n"/>
+      <c r="O175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -4852,6 +5212,8 @@
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
+      <c r="O176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -4867,6 +5229,8 @@
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="2" t="n"/>
+      <c r="N177" s="2" t="n"/>
+      <c r="O177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -4882,6 +5246,8 @@
       <c r="K178" s="2" t="n"/>
       <c r="L178" s="2" t="n"/>
       <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
+      <c r="O178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -4897,6 +5263,8 @@
       <c r="K179" s="2" t="n"/>
       <c r="L179" s="2" t="n"/>
       <c r="M179" s="2" t="n"/>
+      <c r="N179" s="2" t="n"/>
+      <c r="O179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -4912,6 +5280,8 @@
       <c r="K180" s="2" t="n"/>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="n"/>
+      <c r="O180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -4927,6 +5297,8 @@
       <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="2" t="n"/>
+      <c r="N181" s="2" t="n"/>
+      <c r="O181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -4942,6 +5314,8 @@
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="n"/>
+      <c r="O182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -4957,6 +5331,8 @@
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="2" t="n"/>
       <c r="M183" s="2" t="n"/>
+      <c r="N183" s="2" t="n"/>
+      <c r="O183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -4972,6 +5348,8 @@
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
       <c r="M184" s="2" t="n"/>
+      <c r="N184" s="2" t="n"/>
+      <c r="O184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -4987,6 +5365,8 @@
       <c r="K185" s="2" t="n"/>
       <c r="L185" s="2" t="n"/>
       <c r="M185" s="2" t="n"/>
+      <c r="N185" s="2" t="n"/>
+      <c r="O185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -5002,6 +5382,8 @@
       <c r="K186" s="2" t="n"/>
       <c r="L186" s="2" t="n"/>
       <c r="M186" s="2" t="n"/>
+      <c r="N186" s="2" t="n"/>
+      <c r="O186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -5017,6 +5399,8 @@
       <c r="K187" s="2" t="n"/>
       <c r="L187" s="2" t="n"/>
       <c r="M187" s="2" t="n"/>
+      <c r="N187" s="2" t="n"/>
+      <c r="O187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -5032,6 +5416,8 @@
       <c r="K188" s="2" t="n"/>
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="2" t="n"/>
+      <c r="N188" s="2" t="n"/>
+      <c r="O188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -5047,6 +5433,8 @@
       <c r="K189" s="2" t="n"/>
       <c r="L189" s="2" t="n"/>
       <c r="M189" s="2" t="n"/>
+      <c r="N189" s="2" t="n"/>
+      <c r="O189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -5062,6 +5450,8 @@
       <c r="K190" s="2" t="n"/>
       <c r="L190" s="2" t="n"/>
       <c r="M190" s="2" t="n"/>
+      <c r="N190" s="2" t="n"/>
+      <c r="O190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -5077,6 +5467,8 @@
       <c r="K191" s="2" t="n"/>
       <c r="L191" s="2" t="n"/>
       <c r="M191" s="2" t="n"/>
+      <c r="N191" s="2" t="n"/>
+      <c r="O191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -5092,6 +5484,8 @@
       <c r="K192" s="2" t="n"/>
       <c r="L192" s="2" t="n"/>
       <c r="M192" s="2" t="n"/>
+      <c r="N192" s="2" t="n"/>
+      <c r="O192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -5107,6 +5501,8 @@
       <c r="K193" s="2" t="n"/>
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="2" t="n"/>
+      <c r="N193" s="2" t="n"/>
+      <c r="O193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -5122,6 +5518,8 @@
       <c r="K194" s="2" t="n"/>
       <c r="L194" s="2" t="n"/>
       <c r="M194" s="2" t="n"/>
+      <c r="N194" s="2" t="n"/>
+      <c r="O194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -5137,6 +5535,8 @@
       <c r="K195" s="2" t="n"/>
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="2" t="n"/>
+      <c r="N195" s="2" t="n"/>
+      <c r="O195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -5152,6 +5552,8 @@
       <c r="K196" s="2" t="n"/>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="2" t="n"/>
+      <c r="N196" s="2" t="n"/>
+      <c r="O196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -5167,6 +5569,8 @@
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="2" t="n"/>
       <c r="M197" s="2" t="n"/>
+      <c r="N197" s="2" t="n"/>
+      <c r="O197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -5182,6 +5586,8 @@
       <c r="K198" s="2" t="n"/>
       <c r="L198" s="2" t="n"/>
       <c r="M198" s="2" t="n"/>
+      <c r="N198" s="2" t="n"/>
+      <c r="O198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -5197,6 +5603,8 @@
       <c r="K199" s="2" t="n"/>
       <c r="L199" s="2" t="n"/>
       <c r="M199" s="2" t="n"/>
+      <c r="N199" s="2" t="n"/>
+      <c r="O199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -5212,6 +5620,8 @@
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="2" t="n"/>
       <c r="M200" s="2" t="n"/>
+      <c r="N200" s="2" t="n"/>
+      <c r="O200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -5227,6 +5637,8 @@
       <c r="K201" s="2" t="n"/>
       <c r="L201" s="2" t="n"/>
       <c r="M201" s="2" t="n"/>
+      <c r="N201" s="2" t="n"/>
+      <c r="O201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -5242,6 +5654,8 @@
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="2" t="n"/>
+      <c r="N202" s="2" t="n"/>
+      <c r="O202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -5257,6 +5671,8 @@
       <c r="K203" s="2" t="n"/>
       <c r="L203" s="2" t="n"/>
       <c r="M203" s="2" t="n"/>
+      <c r="N203" s="2" t="n"/>
+      <c r="O203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -5272,6 +5688,8 @@
       <c r="K204" s="2" t="n"/>
       <c r="L204" s="2" t="n"/>
       <c r="M204" s="2" t="n"/>
+      <c r="N204" s="2" t="n"/>
+      <c r="O204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -5287,6 +5705,8 @@
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="n"/>
       <c r="M205" s="2" t="n"/>
+      <c r="N205" s="2" t="n"/>
+      <c r="O205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -5302,6 +5722,8 @@
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
       <c r="M206" s="2" t="n"/>
+      <c r="N206" s="2" t="n"/>
+      <c r="O206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -5317,6 +5739,8 @@
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="2" t="n"/>
+      <c r="N207" s="2" t="n"/>
+      <c r="O207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -5332,6 +5756,8 @@
       <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="n"/>
       <c r="M208" s="2" t="n"/>
+      <c r="N208" s="2" t="n"/>
+      <c r="O208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -5347,6 +5773,8 @@
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="2" t="n"/>
+      <c r="N209" s="2" t="n"/>
+      <c r="O209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -5362,6 +5790,8 @@
       <c r="K210" s="2" t="n"/>
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="2" t="n"/>
+      <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -5377,6 +5807,8 @@
       <c r="K211" s="2" t="n"/>
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="2" t="n"/>
+      <c r="N211" s="2" t="n"/>
+      <c r="O211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -5392,6 +5824,8 @@
       <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="2" t="n"/>
+      <c r="N212" s="2" t="n"/>
+      <c r="O212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -5407,6 +5841,8 @@
       <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="2" t="n"/>
+      <c r="N213" s="2" t="n"/>
+      <c r="O213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -5422,6 +5858,8 @@
       <c r="K214" s="2" t="n"/>
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="2" t="n"/>
+      <c r="N214" s="2" t="n"/>
+      <c r="O214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -5437,6 +5875,8 @@
       <c r="K215" s="2" t="n"/>
       <c r="L215" s="2" t="n"/>
       <c r="M215" s="2" t="n"/>
+      <c r="N215" s="2" t="n"/>
+      <c r="O215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -5452,6 +5892,8 @@
       <c r="K216" s="2" t="n"/>
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="2" t="n"/>
+      <c r="N216" s="2" t="n"/>
+      <c r="O216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -5467,6 +5909,8 @@
       <c r="K217" s="2" t="n"/>
       <c r="L217" s="2" t="n"/>
       <c r="M217" s="2" t="n"/>
+      <c r="N217" s="2" t="n"/>
+      <c r="O217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -5482,6 +5926,8 @@
       <c r="K218" s="2" t="n"/>
       <c r="L218" s="2" t="n"/>
       <c r="M218" s="2" t="n"/>
+      <c r="N218" s="2" t="n"/>
+      <c r="O218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -5497,6 +5943,8 @@
       <c r="K219" s="2" t="n"/>
       <c r="L219" s="2" t="n"/>
       <c r="M219" s="2" t="n"/>
+      <c r="N219" s="2" t="n"/>
+      <c r="O219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -5512,6 +5960,8 @@
       <c r="K220" s="2" t="n"/>
       <c r="L220" s="2" t="n"/>
       <c r="M220" s="2" t="n"/>
+      <c r="N220" s="2" t="n"/>
+      <c r="O220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -5527,6 +5977,8 @@
       <c r="K221" s="2" t="n"/>
       <c r="L221" s="2" t="n"/>
       <c r="M221" s="2" t="n"/>
+      <c r="N221" s="2" t="n"/>
+      <c r="O221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -5542,6 +5994,8 @@
       <c r="K222" s="2" t="n"/>
       <c r="L222" s="2" t="n"/>
       <c r="M222" s="2" t="n"/>
+      <c r="N222" s="2" t="n"/>
+      <c r="O222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -5557,6 +6011,8 @@
       <c r="K223" s="2" t="n"/>
       <c r="L223" s="2" t="n"/>
       <c r="M223" s="2" t="n"/>
+      <c r="N223" s="2" t="n"/>
+      <c r="O223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -5572,6 +6028,8 @@
       <c r="K224" s="2" t="n"/>
       <c r="L224" s="2" t="n"/>
       <c r="M224" s="2" t="n"/>
+      <c r="N224" s="2" t="n"/>
+      <c r="O224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -5587,6 +6045,8 @@
       <c r="K225" s="2" t="n"/>
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="2" t="n"/>
+      <c r="N225" s="2" t="n"/>
+      <c r="O225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -5602,6 +6062,8 @@
       <c r="K226" s="2" t="n"/>
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="2" t="n"/>
+      <c r="N226" s="2" t="n"/>
+      <c r="O226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -5617,6 +6079,8 @@
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="2" t="n"/>
+      <c r="N227" s="2" t="n"/>
+      <c r="O227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -5632,6 +6096,8 @@
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="2" t="n"/>
+      <c r="N228" s="2" t="n"/>
+      <c r="O228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -5647,6 +6113,8 @@
       <c r="K229" s="2" t="n"/>
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="2" t="n"/>
+      <c r="N229" s="2" t="n"/>
+      <c r="O229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -5662,6 +6130,8 @@
       <c r="K230" s="2" t="n"/>
       <c r="L230" s="2" t="n"/>
       <c r="M230" s="2" t="n"/>
+      <c r="N230" s="2" t="n"/>
+      <c r="O230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -5677,6 +6147,8 @@
       <c r="K231" s="2" t="n"/>
       <c r="L231" s="2" t="n"/>
       <c r="M231" s="2" t="n"/>
+      <c r="N231" s="2" t="n"/>
+      <c r="O231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -5692,6 +6164,8 @@
       <c r="K232" s="2" t="n"/>
       <c r="L232" s="2" t="n"/>
       <c r="M232" s="2" t="n"/>
+      <c r="N232" s="2" t="n"/>
+      <c r="O232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -5707,6 +6181,8 @@
       <c r="K233" s="2" t="n"/>
       <c r="L233" s="2" t="n"/>
       <c r="M233" s="2" t="n"/>
+      <c r="N233" s="2" t="n"/>
+      <c r="O233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -5722,6 +6198,8 @@
       <c r="K234" s="2" t="n"/>
       <c r="L234" s="2" t="n"/>
       <c r="M234" s="2" t="n"/>
+      <c r="N234" s="2" t="n"/>
+      <c r="O234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -5737,6 +6215,8 @@
       <c r="K235" s="2" t="n"/>
       <c r="L235" s="2" t="n"/>
       <c r="M235" s="2" t="n"/>
+      <c r="N235" s="2" t="n"/>
+      <c r="O235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -5752,6 +6232,8 @@
       <c r="K236" s="2" t="n"/>
       <c r="L236" s="2" t="n"/>
       <c r="M236" s="2" t="n"/>
+      <c r="N236" s="2" t="n"/>
+      <c r="O236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -5767,6 +6249,8 @@
       <c r="K237" s="2" t="n"/>
       <c r="L237" s="2" t="n"/>
       <c r="M237" s="2" t="n"/>
+      <c r="N237" s="2" t="n"/>
+      <c r="O237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -5782,6 +6266,8 @@
       <c r="K238" s="2" t="n"/>
       <c r="L238" s="2" t="n"/>
       <c r="M238" s="2" t="n"/>
+      <c r="N238" s="2" t="n"/>
+      <c r="O238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -5797,6 +6283,8 @@
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="n"/>
       <c r="M239" s="2" t="n"/>
+      <c r="N239" s="2" t="n"/>
+      <c r="O239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -5812,6 +6300,8 @@
       <c r="K240" s="2" t="n"/>
       <c r="L240" s="2" t="n"/>
       <c r="M240" s="2" t="n"/>
+      <c r="N240" s="2" t="n"/>
+      <c r="O240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -5827,6 +6317,8 @@
       <c r="K241" s="2" t="n"/>
       <c r="L241" s="2" t="n"/>
       <c r="M241" s="2" t="n"/>
+      <c r="N241" s="2" t="n"/>
+      <c r="O241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -5842,6 +6334,8 @@
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="n"/>
       <c r="M242" s="2" t="n"/>
+      <c r="N242" s="2" t="n"/>
+      <c r="O242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -5857,6 +6351,8 @@
       <c r="K243" s="2" t="n"/>
       <c r="L243" s="2" t="n"/>
       <c r="M243" s="2" t="n"/>
+      <c r="N243" s="2" t="n"/>
+      <c r="O243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -5872,6 +6368,8 @@
       <c r="K244" s="2" t="n"/>
       <c r="L244" s="2" t="n"/>
       <c r="M244" s="2" t="n"/>
+      <c r="N244" s="2" t="n"/>
+      <c r="O244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -5887,6 +6385,8 @@
       <c r="K245" s="2" t="n"/>
       <c r="L245" s="2" t="n"/>
       <c r="M245" s="2" t="n"/>
+      <c r="N245" s="2" t="n"/>
+      <c r="O245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -5902,6 +6402,8 @@
       <c r="K246" s="2" t="n"/>
       <c r="L246" s="2" t="n"/>
       <c r="M246" s="2" t="n"/>
+      <c r="N246" s="2" t="n"/>
+      <c r="O246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -5917,6 +6419,8 @@
       <c r="K247" s="2" t="n"/>
       <c r="L247" s="2" t="n"/>
       <c r="M247" s="2" t="n"/>
+      <c r="N247" s="2" t="n"/>
+      <c r="O247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -5932,6 +6436,8 @@
       <c r="K248" s="2" t="n"/>
       <c r="L248" s="2" t="n"/>
       <c r="M248" s="2" t="n"/>
+      <c r="N248" s="2" t="n"/>
+      <c r="O248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -5947,6 +6453,8 @@
       <c r="K249" s="2" t="n"/>
       <c r="L249" s="2" t="n"/>
       <c r="M249" s="2" t="n"/>
+      <c r="N249" s="2" t="n"/>
+      <c r="O249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -5962,6 +6470,8 @@
       <c r="K250" s="2" t="n"/>
       <c r="L250" s="2" t="n"/>
       <c r="M250" s="2" t="n"/>
+      <c r="N250" s="2" t="n"/>
+      <c r="O250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -5977,6 +6487,8 @@
       <c r="K251" s="2" t="n"/>
       <c r="L251" s="2" t="n"/>
       <c r="M251" s="2" t="n"/>
+      <c r="N251" s="2" t="n"/>
+      <c r="O251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -5992,6 +6504,8 @@
       <c r="K252" s="2" t="n"/>
       <c r="L252" s="2" t="n"/>
       <c r="M252" s="2" t="n"/>
+      <c r="N252" s="2" t="n"/>
+      <c r="O252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -6007,6 +6521,8 @@
       <c r="K253" s="2" t="n"/>
       <c r="L253" s="2" t="n"/>
       <c r="M253" s="2" t="n"/>
+      <c r="N253" s="2" t="n"/>
+      <c r="O253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -6022,6 +6538,8 @@
       <c r="K254" s="2" t="n"/>
       <c r="L254" s="2" t="n"/>
       <c r="M254" s="2" t="n"/>
+      <c r="N254" s="2" t="n"/>
+      <c r="O254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -6037,6 +6555,8 @@
       <c r="K255" s="2" t="n"/>
       <c r="L255" s="2" t="n"/>
       <c r="M255" s="2" t="n"/>
+      <c r="N255" s="2" t="n"/>
+      <c r="O255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -6052,6 +6572,8 @@
       <c r="K256" s="2" t="n"/>
       <c r="L256" s="2" t="n"/>
       <c r="M256" s="2" t="n"/>
+      <c r="N256" s="2" t="n"/>
+      <c r="O256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -6067,6 +6589,8 @@
       <c r="K257" s="2" t="n"/>
       <c r="L257" s="2" t="n"/>
       <c r="M257" s="2" t="n"/>
+      <c r="N257" s="2" t="n"/>
+      <c r="O257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -6082,6 +6606,8 @@
       <c r="K258" s="2" t="n"/>
       <c r="L258" s="2" t="n"/>
       <c r="M258" s="2" t="n"/>
+      <c r="N258" s="2" t="n"/>
+      <c r="O258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -6097,6 +6623,8 @@
       <c r="K259" s="2" t="n"/>
       <c r="L259" s="2" t="n"/>
       <c r="M259" s="2" t="n"/>
+      <c r="N259" s="2" t="n"/>
+      <c r="O259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -6112,6 +6640,8 @@
       <c r="K260" s="2" t="n"/>
       <c r="L260" s="2" t="n"/>
       <c r="M260" s="2" t="n"/>
+      <c r="N260" s="2" t="n"/>
+      <c r="O260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -6127,6 +6657,8 @@
       <c r="K261" s="2" t="n"/>
       <c r="L261" s="2" t="n"/>
       <c r="M261" s="2" t="n"/>
+      <c r="N261" s="2" t="n"/>
+      <c r="O261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -6142,6 +6674,8 @@
       <c r="K262" s="2" t="n"/>
       <c r="L262" s="2" t="n"/>
       <c r="M262" s="2" t="n"/>
+      <c r="N262" s="2" t="n"/>
+      <c r="O262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -6157,6 +6691,8 @@
       <c r="K263" s="2" t="n"/>
       <c r="L263" s="2" t="n"/>
       <c r="M263" s="2" t="n"/>
+      <c r="N263" s="2" t="n"/>
+      <c r="O263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -6172,6 +6708,8 @@
       <c r="K264" s="2" t="n"/>
       <c r="L264" s="2" t="n"/>
       <c r="M264" s="2" t="n"/>
+      <c r="N264" s="2" t="n"/>
+      <c r="O264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -6187,6 +6725,8 @@
       <c r="K265" s="2" t="n"/>
       <c r="L265" s="2" t="n"/>
       <c r="M265" s="2" t="n"/>
+      <c r="N265" s="2" t="n"/>
+      <c r="O265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -6202,6 +6742,8 @@
       <c r="K266" s="2" t="n"/>
       <c r="L266" s="2" t="n"/>
       <c r="M266" s="2" t="n"/>
+      <c r="N266" s="2" t="n"/>
+      <c r="O266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -6217,6 +6759,8 @@
       <c r="K267" s="2" t="n"/>
       <c r="L267" s="2" t="n"/>
       <c r="M267" s="2" t="n"/>
+      <c r="N267" s="2" t="n"/>
+      <c r="O267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -6232,6 +6776,8 @@
       <c r="K268" s="2" t="n"/>
       <c r="L268" s="2" t="n"/>
       <c r="M268" s="2" t="n"/>
+      <c r="N268" s="2" t="n"/>
+      <c r="O268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -6247,6 +6793,8 @@
       <c r="K269" s="2" t="n"/>
       <c r="L269" s="2" t="n"/>
       <c r="M269" s="2" t="n"/>
+      <c r="N269" s="2" t="n"/>
+      <c r="O269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -6262,6 +6810,8 @@
       <c r="K270" s="2" t="n"/>
       <c r="L270" s="2" t="n"/>
       <c r="M270" s="2" t="n"/>
+      <c r="N270" s="2" t="n"/>
+      <c r="O270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -6277,6 +6827,8 @@
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="2" t="n"/>
       <c r="M271" s="2" t="n"/>
+      <c r="N271" s="2" t="n"/>
+      <c r="O271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -6292,6 +6844,8 @@
       <c r="K272" s="2" t="n"/>
       <c r="L272" s="2" t="n"/>
       <c r="M272" s="2" t="n"/>
+      <c r="N272" s="2" t="n"/>
+      <c r="O272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -6307,6 +6861,8 @@
       <c r="K273" s="2" t="n"/>
       <c r="L273" s="2" t="n"/>
       <c r="M273" s="2" t="n"/>
+      <c r="N273" s="2" t="n"/>
+      <c r="O273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -6322,6 +6878,8 @@
       <c r="K274" s="2" t="n"/>
       <c r="L274" s="2" t="n"/>
       <c r="M274" s="2" t="n"/>
+      <c r="N274" s="2" t="n"/>
+      <c r="O274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -6337,6 +6895,8 @@
       <c r="K275" s="2" t="n"/>
       <c r="L275" s="2" t="n"/>
       <c r="M275" s="2" t="n"/>
+      <c r="N275" s="2" t="n"/>
+      <c r="O275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -6352,6 +6912,8 @@
       <c r="K276" s="2" t="n"/>
       <c r="L276" s="2" t="n"/>
       <c r="M276" s="2" t="n"/>
+      <c r="N276" s="2" t="n"/>
+      <c r="O276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -6367,6 +6929,8 @@
       <c r="K277" s="2" t="n"/>
       <c r="L277" s="2" t="n"/>
       <c r="M277" s="2" t="n"/>
+      <c r="N277" s="2" t="n"/>
+      <c r="O277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -6382,6 +6946,8 @@
       <c r="K278" s="2" t="n"/>
       <c r="L278" s="2" t="n"/>
       <c r="M278" s="2" t="n"/>
+      <c r="N278" s="2" t="n"/>
+      <c r="O278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -6397,6 +6963,8 @@
       <c r="K279" s="2" t="n"/>
       <c r="L279" s="2" t="n"/>
       <c r="M279" s="2" t="n"/>
+      <c r="N279" s="2" t="n"/>
+      <c r="O279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -6412,6 +6980,8 @@
       <c r="K280" s="2" t="n"/>
       <c r="L280" s="2" t="n"/>
       <c r="M280" s="2" t="n"/>
+      <c r="N280" s="2" t="n"/>
+      <c r="O280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -6427,6 +6997,8 @@
       <c r="K281" s="2" t="n"/>
       <c r="L281" s="2" t="n"/>
       <c r="M281" s="2" t="n"/>
+      <c r="N281" s="2" t="n"/>
+      <c r="O281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -6442,6 +7014,8 @@
       <c r="K282" s="2" t="n"/>
       <c r="L282" s="2" t="n"/>
       <c r="M282" s="2" t="n"/>
+      <c r="N282" s="2" t="n"/>
+      <c r="O282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -6457,6 +7031,8 @@
       <c r="K283" s="2" t="n"/>
       <c r="L283" s="2" t="n"/>
       <c r="M283" s="2" t="n"/>
+      <c r="N283" s="2" t="n"/>
+      <c r="O283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -6472,6 +7048,8 @@
       <c r="K284" s="2" t="n"/>
       <c r="L284" s="2" t="n"/>
       <c r="M284" s="2" t="n"/>
+      <c r="N284" s="2" t="n"/>
+      <c r="O284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -6487,6 +7065,8 @@
       <c r="K285" s="2" t="n"/>
       <c r="L285" s="2" t="n"/>
       <c r="M285" s="2" t="n"/>
+      <c r="N285" s="2" t="n"/>
+      <c r="O285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -6502,6 +7082,8 @@
       <c r="K286" s="2" t="n"/>
       <c r="L286" s="2" t="n"/>
       <c r="M286" s="2" t="n"/>
+      <c r="N286" s="2" t="n"/>
+      <c r="O286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -6517,6 +7099,8 @@
       <c r="K287" s="2" t="n"/>
       <c r="L287" s="2" t="n"/>
       <c r="M287" s="2" t="n"/>
+      <c r="N287" s="2" t="n"/>
+      <c r="O287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -6532,6 +7116,8 @@
       <c r="K288" s="2" t="n"/>
       <c r="L288" s="2" t="n"/>
       <c r="M288" s="2" t="n"/>
+      <c r="N288" s="2" t="n"/>
+      <c r="O288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -6547,6 +7133,8 @@
       <c r="K289" s="2" t="n"/>
       <c r="L289" s="2" t="n"/>
       <c r="M289" s="2" t="n"/>
+      <c r="N289" s="2" t="n"/>
+      <c r="O289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -6562,6 +7150,8 @@
       <c r="K290" s="2" t="n"/>
       <c r="L290" s="2" t="n"/>
       <c r="M290" s="2" t="n"/>
+      <c r="N290" s="2" t="n"/>
+      <c r="O290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -6577,6 +7167,8 @@
       <c r="K291" s="2" t="n"/>
       <c r="L291" s="2" t="n"/>
       <c r="M291" s="2" t="n"/>
+      <c r="N291" s="2" t="n"/>
+      <c r="O291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -6592,6 +7184,8 @@
       <c r="K292" s="2" t="n"/>
       <c r="L292" s="2" t="n"/>
       <c r="M292" s="2" t="n"/>
+      <c r="N292" s="2" t="n"/>
+      <c r="O292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -6607,6 +7201,8 @@
       <c r="K293" s="2" t="n"/>
       <c r="L293" s="2" t="n"/>
       <c r="M293" s="2" t="n"/>
+      <c r="N293" s="2" t="n"/>
+      <c r="O293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -6622,6 +7218,8 @@
       <c r="K294" s="2" t="n"/>
       <c r="L294" s="2" t="n"/>
       <c r="M294" s="2" t="n"/>
+      <c r="N294" s="2" t="n"/>
+      <c r="O294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -6637,6 +7235,8 @@
       <c r="K295" s="2" t="n"/>
       <c r="L295" s="2" t="n"/>
       <c r="M295" s="2" t="n"/>
+      <c r="N295" s="2" t="n"/>
+      <c r="O295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -6652,6 +7252,8 @@
       <c r="K296" s="2" t="n"/>
       <c r="L296" s="2" t="n"/>
       <c r="M296" s="2" t="n"/>
+      <c r="N296" s="2" t="n"/>
+      <c r="O296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -6667,6 +7269,8 @@
       <c r="K297" s="2" t="n"/>
       <c r="L297" s="2" t="n"/>
       <c r="M297" s="2" t="n"/>
+      <c r="N297" s="2" t="n"/>
+      <c r="O297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -6682,6 +7286,8 @@
       <c r="K298" s="2" t="n"/>
       <c r="L298" s="2" t="n"/>
       <c r="M298" s="2" t="n"/>
+      <c r="N298" s="2" t="n"/>
+      <c r="O298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -6697,6 +7303,8 @@
       <c r="K299" s="2" t="n"/>
       <c r="L299" s="2" t="n"/>
       <c r="M299" s="2" t="n"/>
+      <c r="N299" s="2" t="n"/>
+      <c r="O299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -6712,6 +7320,8 @@
       <c r="K300" s="2" t="n"/>
       <c r="L300" s="2" t="n"/>
       <c r="M300" s="2" t="n"/>
+      <c r="N300" s="2" t="n"/>
+      <c r="O300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -6727,9 +7337,11 @@
       <c r="K301" s="2" t="n"/>
       <c r="L301" s="2" t="n"/>
       <c r="M301" s="2" t="n"/>
+      <c r="N301" s="2" t="n"/>
+      <c r="O301" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M301"/>
+  <autoFilter ref="A1:O301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11351,7 +11963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:K301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11362,6 +11974,9 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11405,6 +12020,21 @@
           <t>출처</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>제품구분</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>품목유형코드</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>품목유형명</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -11415,6 +12045,9 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -11425,6 +12058,9 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -11435,6 +12071,9 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -11445,6 +12084,9 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -11455,6 +12097,9 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -11465,6 +12110,9 @@
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -11475,6 +12123,9 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -11485,6 +12136,9 @@
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -11495,6 +12149,9 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -11505,6 +12162,9 @@
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -11515,6 +12175,9 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -11525,6 +12188,9 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -11535,6 +12201,9 @@
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -11545,6 +12214,9 @@
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -11555,6 +12227,9 @@
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -11565,6 +12240,9 @@
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -11575,6 +12253,9 @@
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -11585,6 +12266,9 @@
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -11595,6 +12279,9 @@
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -11605,6 +12292,9 @@
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -11615,6 +12305,9 @@
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -11625,6 +12318,9 @@
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -11635,6 +12331,9 @@
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -11645,6 +12344,9 @@
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -11655,6 +12357,9 @@
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -11665,6 +12370,9 @@
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -11675,6 +12383,9 @@
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -11685,6 +12396,9 @@
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -11695,6 +12409,9 @@
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -11705,6 +12422,9 @@
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -11715,6 +12435,9 @@
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -11725,6 +12448,9 @@
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -11735,6 +12461,9 @@
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -11745,6 +12474,9 @@
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -11755,6 +12487,9 @@
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -11765,6 +12500,9 @@
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -11775,6 +12513,9 @@
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -11785,6 +12526,9 @@
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -11795,6 +12539,9 @@
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -11805,6 +12552,9 @@
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -11815,6 +12565,9 @@
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -11825,6 +12578,9 @@
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -11835,6 +12591,9 @@
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -11845,6 +12604,9 @@
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -11855,6 +12617,9 @@
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -11865,6 +12630,9 @@
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -11875,6 +12643,9 @@
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -11885,6 +12656,9 @@
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -11895,6 +12669,9 @@
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -11905,6 +12682,9 @@
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -11915,6 +12695,9 @@
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -11925,6 +12708,9 @@
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -11935,6 +12721,9 @@
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -11945,6 +12734,9 @@
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -11955,6 +12747,9 @@
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -11965,6 +12760,9 @@
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -11975,6 +12773,9 @@
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -11985,6 +12786,9 @@
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -11995,6 +12799,9 @@
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -12005,6 +12812,9 @@
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -12015,6 +12825,9 @@
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -12025,6 +12838,9 @@
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -12035,6 +12851,9 @@
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -12045,6 +12864,9 @@
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -12055,6 +12877,9 @@
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -12065,6 +12890,9 @@
       <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -12075,6 +12903,9 @@
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -12085,6 +12916,9 @@
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -12095,6 +12929,9 @@
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -12105,6 +12942,9 @@
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -12115,6 +12955,9 @@
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -12125,6 +12968,9 @@
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -12135,6 +12981,9 @@
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -12145,6 +12994,9 @@
       <c r="F75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -12155,6 +13007,9 @@
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -12165,6 +13020,9 @@
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
       <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -12175,6 +13033,9 @@
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -12185,6 +13046,9 @@
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -12195,6 +13059,9 @@
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -12205,6 +13072,9 @@
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -12215,6 +13085,9 @@
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -12225,6 +13098,9 @@
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -12235,6 +13111,9 @@
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -12245,6 +13124,9 @@
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -12255,6 +13137,9 @@
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -12265,6 +13150,9 @@
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -12275,6 +13163,9 @@
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -12285,6 +13176,9 @@
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -12295,6 +13189,9 @@
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -12305,6 +13202,9 @@
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n"/>
+      <c r="K91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -12315,6 +13215,9 @@
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -12325,6 +13228,9 @@
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -12335,6 +13241,9 @@
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -12345,6 +13254,9 @@
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -12355,6 +13267,9 @@
       <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -12365,6 +13280,9 @@
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -12375,6 +13293,9 @@
       <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -12385,6 +13306,9 @@
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n"/>
+      <c r="K99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -12395,6 +13319,9 @@
       <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -12405,6 +13332,9 @@
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -12415,6 +13345,9 @@
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -12425,6 +13358,9 @@
       <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -12435,6 +13371,9 @@
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -12445,6 +13384,9 @@
       <c r="F105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n"/>
+      <c r="K105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -12455,6 +13397,9 @@
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
       <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -12465,6 +13410,9 @@
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -12475,6 +13423,9 @@
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -12485,6 +13436,9 @@
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -12495,6 +13449,9 @@
       <c r="F110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -12505,6 +13462,9 @@
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
+      <c r="I111" s="2" t="n"/>
+      <c r="J111" s="2" t="n"/>
+      <c r="K111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -12515,6 +13475,9 @@
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -12525,6 +13488,9 @@
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -12535,6 +13501,9 @@
       <c r="F114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -12545,6 +13514,9 @@
       <c r="F115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -12555,6 +13527,9 @@
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -12565,6 +13540,9 @@
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -12575,6 +13553,9 @@
       <c r="F118" s="2" t="n"/>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -12585,6 +13566,9 @@
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -12595,6 +13579,9 @@
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -12605,6 +13592,9 @@
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="n"/>
+      <c r="K121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -12615,6 +13605,9 @@
       <c r="F122" s="2" t="n"/>
       <c r="G122" s="2" t="n"/>
       <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -12625,6 +13618,9 @@
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="n"/>
+      <c r="K123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -12635,6 +13631,9 @@
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -12645,6 +13644,9 @@
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
+      <c r="I125" s="2" t="n"/>
+      <c r="J125" s="2" t="n"/>
+      <c r="K125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -12655,6 +13657,9 @@
       <c r="F126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -12665,6 +13670,9 @@
       <c r="F127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="n"/>
+      <c r="K127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -12675,6 +13683,9 @@
       <c r="F128" s="2" t="n"/>
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -12685,6 +13696,9 @@
       <c r="F129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -12695,6 +13709,9 @@
       <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -12705,6 +13722,9 @@
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
+      <c r="K131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -12715,6 +13735,9 @@
       <c r="F132" s="2" t="n"/>
       <c r="G132" s="2" t="n"/>
       <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -12725,6 +13748,9 @@
       <c r="F133" s="2" t="n"/>
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+      <c r="J133" s="2" t="n"/>
+      <c r="K133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -12735,6 +13761,9 @@
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -12745,6 +13774,9 @@
       <c r="F135" s="2" t="n"/>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
+      <c r="K135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -12755,6 +13787,9 @@
       <c r="F136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
+      <c r="I136" s="2" t="n"/>
+      <c r="J136" s="2" t="n"/>
+      <c r="K136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -12765,6 +13800,9 @@
       <c r="F137" s="2" t="n"/>
       <c r="G137" s="2" t="n"/>
       <c r="H137" s="2" t="n"/>
+      <c r="I137" s="2" t="n"/>
+      <c r="J137" s="2" t="n"/>
+      <c r="K137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -12775,6 +13813,9 @@
       <c r="F138" s="2" t="n"/>
       <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
+      <c r="K138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -12785,6 +13826,9 @@
       <c r="F139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="n"/>
+      <c r="K139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -12795,6 +13839,9 @@
       <c r="F140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
+      <c r="J140" s="2" t="n"/>
+      <c r="K140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -12805,6 +13852,9 @@
       <c r="F141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
+      <c r="I141" s="2" t="n"/>
+      <c r="J141" s="2" t="n"/>
+      <c r="K141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -12815,6 +13865,9 @@
       <c r="F142" s="2" t="n"/>
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -12825,6 +13878,9 @@
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
+      <c r="J143" s="2" t="n"/>
+      <c r="K143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -12835,6 +13891,9 @@
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -12845,6 +13904,9 @@
       <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -12855,6 +13917,9 @@
       <c r="F146" s="2" t="n"/>
       <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -12865,6 +13930,9 @@
       <c r="F147" s="2" t="n"/>
       <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
+      <c r="I147" s="2" t="n"/>
+      <c r="J147" s="2" t="n"/>
+      <c r="K147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -12875,6 +13943,9 @@
       <c r="F148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
+      <c r="K148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -12885,6 +13956,9 @@
       <c r="F149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="n"/>
+      <c r="K149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -12895,6 +13969,9 @@
       <c r="F150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -12905,6 +13982,9 @@
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
+      <c r="I151" s="2" t="n"/>
+      <c r="J151" s="2" t="n"/>
+      <c r="K151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -12915,6 +13995,9 @@
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -12925,6 +14008,9 @@
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
+      <c r="J153" s="2" t="n"/>
+      <c r="K153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -12935,6 +14021,9 @@
       <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
+      <c r="K154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -12945,6 +14034,9 @@
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
+      <c r="I155" s="2" t="n"/>
+      <c r="J155" s="2" t="n"/>
+      <c r="K155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -12955,6 +14047,9 @@
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
+      <c r="K156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -12965,6 +14060,9 @@
       <c r="F157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
+      <c r="I157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -12975,6 +14073,9 @@
       <c r="F158" s="2" t="n"/>
       <c r="G158" s="2" t="n"/>
       <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -12985,6 +14086,9 @@
       <c r="F159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
+      <c r="J159" s="2" t="n"/>
+      <c r="K159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -12995,6 +14099,9 @@
       <c r="F160" s="2" t="n"/>
       <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="n"/>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="n"/>
+      <c r="K160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -13005,6 +14112,9 @@
       <c r="F161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
+      <c r="J161" s="2" t="n"/>
+      <c r="K161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -13015,6 +14125,9 @@
       <c r="F162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="n"/>
+      <c r="K162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -13025,6 +14138,9 @@
       <c r="F163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2" t="n"/>
+      <c r="J163" s="2" t="n"/>
+      <c r="K163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -13035,6 +14151,9 @@
       <c r="F164" s="2" t="n"/>
       <c r="G164" s="2" t="n"/>
       <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="n"/>
+      <c r="J164" s="2" t="n"/>
+      <c r="K164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -13045,6 +14164,9 @@
       <c r="F165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="n"/>
+      <c r="K165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -13055,6 +14177,9 @@
       <c r="F166" s="2" t="n"/>
       <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -13065,6 +14190,9 @@
       <c r="F167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="n"/>
+      <c r="K167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -13075,6 +14203,9 @@
       <c r="F168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -13085,6 +14216,9 @@
       <c r="F169" s="2" t="n"/>
       <c r="G169" s="2" t="n"/>
       <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
+      <c r="K169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -13095,6 +14229,9 @@
       <c r="F170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
+      <c r="K170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -13105,6 +14242,9 @@
       <c r="F171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
+      <c r="I171" s="2" t="n"/>
+      <c r="J171" s="2" t="n"/>
+      <c r="K171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -13115,6 +14255,9 @@
       <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="n"/>
+      <c r="K172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -13125,6 +14268,9 @@
       <c r="F173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
+      <c r="I173" s="2" t="n"/>
+      <c r="J173" s="2" t="n"/>
+      <c r="K173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -13135,6 +14281,9 @@
       <c r="F174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
+      <c r="I174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
+      <c r="K174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -13145,6 +14294,9 @@
       <c r="F175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
+      <c r="I175" s="2" t="n"/>
+      <c r="J175" s="2" t="n"/>
+      <c r="K175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -13155,6 +14307,9 @@
       <c r="F176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="n"/>
+      <c r="K176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -13165,6 +14320,9 @@
       <c r="F177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
+      <c r="I177" s="2" t="n"/>
+      <c r="J177" s="2" t="n"/>
+      <c r="K177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -13175,6 +14333,9 @@
       <c r="F178" s="2" t="n"/>
       <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
+      <c r="K178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -13185,6 +14346,9 @@
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="n"/>
+      <c r="K179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -13195,6 +14359,9 @@
       <c r="F180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
+      <c r="K180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -13205,6 +14372,9 @@
       <c r="F181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="n"/>
+      <c r="K181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -13215,6 +14385,9 @@
       <c r="F182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
+      <c r="K182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -13225,6 +14398,9 @@
       <c r="F183" s="2" t="n"/>
       <c r="G183" s="2" t="n"/>
       <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+      <c r="J183" s="2" t="n"/>
+      <c r="K183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -13235,6 +14411,9 @@
       <c r="F184" s="2" t="n"/>
       <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="n"/>
+      <c r="K184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -13245,6 +14424,9 @@
       <c r="F185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
+      <c r="I185" s="2" t="n"/>
+      <c r="J185" s="2" t="n"/>
+      <c r="K185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -13255,6 +14437,9 @@
       <c r="F186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+      <c r="J186" s="2" t="n"/>
+      <c r="K186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -13265,6 +14450,9 @@
       <c r="F187" s="2" t="n"/>
       <c r="G187" s="2" t="n"/>
       <c r="H187" s="2" t="n"/>
+      <c r="I187" s="2" t="n"/>
+      <c r="J187" s="2" t="n"/>
+      <c r="K187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -13275,6 +14463,9 @@
       <c r="F188" s="2" t="n"/>
       <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2" t="n"/>
+      <c r="J188" s="2" t="n"/>
+      <c r="K188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -13285,6 +14476,9 @@
       <c r="F189" s="2" t="n"/>
       <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
+      <c r="I189" s="2" t="n"/>
+      <c r="J189" s="2" t="n"/>
+      <c r="K189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -13295,6 +14489,9 @@
       <c r="F190" s="2" t="n"/>
       <c r="G190" s="2" t="n"/>
       <c r="H190" s="2" t="n"/>
+      <c r="I190" s="2" t="n"/>
+      <c r="J190" s="2" t="n"/>
+      <c r="K190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -13305,6 +14502,9 @@
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
+      <c r="I191" s="2" t="n"/>
+      <c r="J191" s="2" t="n"/>
+      <c r="K191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -13315,6 +14515,9 @@
       <c r="F192" s="2" t="n"/>
       <c r="G192" s="2" t="n"/>
       <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2" t="n"/>
+      <c r="J192" s="2" t="n"/>
+      <c r="K192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -13325,6 +14528,9 @@
       <c r="F193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
+      <c r="I193" s="2" t="n"/>
+      <c r="J193" s="2" t="n"/>
+      <c r="K193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -13335,6 +14541,9 @@
       <c r="F194" s="2" t="n"/>
       <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
+      <c r="I194" s="2" t="n"/>
+      <c r="J194" s="2" t="n"/>
+      <c r="K194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -13345,6 +14554,9 @@
       <c r="F195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
+      <c r="I195" s="2" t="n"/>
+      <c r="J195" s="2" t="n"/>
+      <c r="K195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -13355,6 +14567,9 @@
       <c r="F196" s="2" t="n"/>
       <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="n"/>
+      <c r="K196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -13365,6 +14580,9 @@
       <c r="F197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
+      <c r="J197" s="2" t="n"/>
+      <c r="K197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -13375,6 +14593,9 @@
       <c r="F198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+      <c r="J198" s="2" t="n"/>
+      <c r="K198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -13385,6 +14606,9 @@
       <c r="F199" s="2" t="n"/>
       <c r="G199" s="2" t="n"/>
       <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -13395,6 +14619,9 @@
       <c r="F200" s="2" t="n"/>
       <c r="G200" s="2" t="n"/>
       <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+      <c r="J200" s="2" t="n"/>
+      <c r="K200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -13405,6 +14632,9 @@
       <c r="F201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
+      <c r="K201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -13415,6 +14645,9 @@
       <c r="F202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
+      <c r="K202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -13425,6 +14658,9 @@
       <c r="F203" s="2" t="n"/>
       <c r="G203" s="2" t="n"/>
       <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+      <c r="J203" s="2" t="n"/>
+      <c r="K203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -13435,6 +14671,9 @@
       <c r="F204" s="2" t="n"/>
       <c r="G204" s="2" t="n"/>
       <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -13445,6 +14684,9 @@
       <c r="F205" s="2" t="n"/>
       <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
+      <c r="J205" s="2" t="n"/>
+      <c r="K205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -13455,6 +14697,9 @@
       <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="n"/>
+      <c r="K206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -13465,6 +14710,9 @@
       <c r="F207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="n"/>
+      <c r="K207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -13475,6 +14723,9 @@
       <c r="F208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -13485,6 +14736,9 @@
       <c r="F209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
+      <c r="I209" s="2" t="n"/>
+      <c r="J209" s="2" t="n"/>
+      <c r="K209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -13495,6 +14749,9 @@
       <c r="F210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="n"/>
+      <c r="K210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -13505,6 +14762,9 @@
       <c r="F211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
+      <c r="I211" s="2" t="n"/>
+      <c r="J211" s="2" t="n"/>
+      <c r="K211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -13515,6 +14775,9 @@
       <c r="F212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="n"/>
+      <c r="K212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -13525,6 +14788,9 @@
       <c r="F213" s="2" t="n"/>
       <c r="G213" s="2" t="n"/>
       <c r="H213" s="2" t="n"/>
+      <c r="I213" s="2" t="n"/>
+      <c r="J213" s="2" t="n"/>
+      <c r="K213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -13535,6 +14801,9 @@
       <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -13545,6 +14814,9 @@
       <c r="F215" s="2" t="n"/>
       <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
+      <c r="J215" s="2" t="n"/>
+      <c r="K215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -13555,6 +14827,9 @@
       <c r="F216" s="2" t="n"/>
       <c r="G216" s="2" t="n"/>
       <c r="H216" s="2" t="n"/>
+      <c r="I216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
+      <c r="K216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -13565,6 +14840,9 @@
       <c r="F217" s="2" t="n"/>
       <c r="G217" s="2" t="n"/>
       <c r="H217" s="2" t="n"/>
+      <c r="I217" s="2" t="n"/>
+      <c r="J217" s="2" t="n"/>
+      <c r="K217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -13575,6 +14853,9 @@
       <c r="F218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="H218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
+      <c r="J218" s="2" t="n"/>
+      <c r="K218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -13585,6 +14866,9 @@
       <c r="F219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="H219" s="2" t="n"/>
+      <c r="I219" s="2" t="n"/>
+      <c r="J219" s="2" t="n"/>
+      <c r="K219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -13595,6 +14879,9 @@
       <c r="F220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="H220" s="2" t="n"/>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
+      <c r="K220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -13605,6 +14892,9 @@
       <c r="F221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="H221" s="2" t="n"/>
+      <c r="I221" s="2" t="n"/>
+      <c r="J221" s="2" t="n"/>
+      <c r="K221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -13615,6 +14905,9 @@
       <c r="F222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="H222" s="2" t="n"/>
+      <c r="I222" s="2" t="n"/>
+      <c r="J222" s="2" t="n"/>
+      <c r="K222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -13625,6 +14918,9 @@
       <c r="F223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="H223" s="2" t="n"/>
+      <c r="I223" s="2" t="n"/>
+      <c r="J223" s="2" t="n"/>
+      <c r="K223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -13635,6 +14931,9 @@
       <c r="F224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="H224" s="2" t="n"/>
+      <c r="I224" s="2" t="n"/>
+      <c r="J224" s="2" t="n"/>
+      <c r="K224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -13645,6 +14944,9 @@
       <c r="F225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="H225" s="2" t="n"/>
+      <c r="I225" s="2" t="n"/>
+      <c r="J225" s="2" t="n"/>
+      <c r="K225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -13655,6 +14957,9 @@
       <c r="F226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="H226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+      <c r="J226" s="2" t="n"/>
+      <c r="K226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -13665,6 +14970,9 @@
       <c r="F227" s="2" t="n"/>
       <c r="G227" s="2" t="n"/>
       <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+      <c r="J227" s="2" t="n"/>
+      <c r="K227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -13675,6 +14983,9 @@
       <c r="F228" s="2" t="n"/>
       <c r="G228" s="2" t="n"/>
       <c r="H228" s="2" t="n"/>
+      <c r="I228" s="2" t="n"/>
+      <c r="J228" s="2" t="n"/>
+      <c r="K228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -13685,6 +14996,9 @@
       <c r="F229" s="2" t="n"/>
       <c r="G229" s="2" t="n"/>
       <c r="H229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+      <c r="J229" s="2" t="n"/>
+      <c r="K229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -13695,6 +15009,9 @@
       <c r="F230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="H230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+      <c r="J230" s="2" t="n"/>
+      <c r="K230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -13705,6 +15022,9 @@
       <c r="F231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
+      <c r="K231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -13715,6 +15035,9 @@
       <c r="F232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="H232" s="2" t="n"/>
+      <c r="I232" s="2" t="n"/>
+      <c r="J232" s="2" t="n"/>
+      <c r="K232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -13725,6 +15048,9 @@
       <c r="F233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
       <c r="H233" s="2" t="n"/>
+      <c r="I233" s="2" t="n"/>
+      <c r="J233" s="2" t="n"/>
+      <c r="K233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -13735,6 +15061,9 @@
       <c r="F234" s="2" t="n"/>
       <c r="G234" s="2" t="n"/>
       <c r="H234" s="2" t="n"/>
+      <c r="I234" s="2" t="n"/>
+      <c r="J234" s="2" t="n"/>
+      <c r="K234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -13745,6 +15074,9 @@
       <c r="F235" s="2" t="n"/>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
+      <c r="I235" s="2" t="n"/>
+      <c r="J235" s="2" t="n"/>
+      <c r="K235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -13755,6 +15087,9 @@
       <c r="F236" s="2" t="n"/>
       <c r="G236" s="2" t="n"/>
       <c r="H236" s="2" t="n"/>
+      <c r="I236" s="2" t="n"/>
+      <c r="J236" s="2" t="n"/>
+      <c r="K236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -13765,6 +15100,9 @@
       <c r="F237" s="2" t="n"/>
       <c r="G237" s="2" t="n"/>
       <c r="H237" s="2" t="n"/>
+      <c r="I237" s="2" t="n"/>
+      <c r="J237" s="2" t="n"/>
+      <c r="K237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -13775,6 +15113,9 @@
       <c r="F238" s="2" t="n"/>
       <c r="G238" s="2" t="n"/>
       <c r="H238" s="2" t="n"/>
+      <c r="I238" s="2" t="n"/>
+      <c r="J238" s="2" t="n"/>
+      <c r="K238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -13785,6 +15126,9 @@
       <c r="F239" s="2" t="n"/>
       <c r="G239" s="2" t="n"/>
       <c r="H239" s="2" t="n"/>
+      <c r="I239" s="2" t="n"/>
+      <c r="J239" s="2" t="n"/>
+      <c r="K239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -13795,6 +15139,9 @@
       <c r="F240" s="2" t="n"/>
       <c r="G240" s="2" t="n"/>
       <c r="H240" s="2" t="n"/>
+      <c r="I240" s="2" t="n"/>
+      <c r="J240" s="2" t="n"/>
+      <c r="K240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -13805,6 +15152,9 @@
       <c r="F241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="H241" s="2" t="n"/>
+      <c r="I241" s="2" t="n"/>
+      <c r="J241" s="2" t="n"/>
+      <c r="K241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -13815,6 +15165,9 @@
       <c r="F242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="H242" s="2" t="n"/>
+      <c r="I242" s="2" t="n"/>
+      <c r="J242" s="2" t="n"/>
+      <c r="K242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -13825,6 +15178,9 @@
       <c r="F243" s="2" t="n"/>
       <c r="G243" s="2" t="n"/>
       <c r="H243" s="2" t="n"/>
+      <c r="I243" s="2" t="n"/>
+      <c r="J243" s="2" t="n"/>
+      <c r="K243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -13835,6 +15191,9 @@
       <c r="F244" s="2" t="n"/>
       <c r="G244" s="2" t="n"/>
       <c r="H244" s="2" t="n"/>
+      <c r="I244" s="2" t="n"/>
+      <c r="J244" s="2" t="n"/>
+      <c r="K244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -13845,6 +15204,9 @@
       <c r="F245" s="2" t="n"/>
       <c r="G245" s="2" t="n"/>
       <c r="H245" s="2" t="n"/>
+      <c r="I245" s="2" t="n"/>
+      <c r="J245" s="2" t="n"/>
+      <c r="K245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -13855,6 +15217,9 @@
       <c r="F246" s="2" t="n"/>
       <c r="G246" s="2" t="n"/>
       <c r="H246" s="2" t="n"/>
+      <c r="I246" s="2" t="n"/>
+      <c r="J246" s="2" t="n"/>
+      <c r="K246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -13865,6 +15230,9 @@
       <c r="F247" s="2" t="n"/>
       <c r="G247" s="2" t="n"/>
       <c r="H247" s="2" t="n"/>
+      <c r="I247" s="2" t="n"/>
+      <c r="J247" s="2" t="n"/>
+      <c r="K247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -13875,6 +15243,9 @@
       <c r="F248" s="2" t="n"/>
       <c r="G248" s="2" t="n"/>
       <c r="H248" s="2" t="n"/>
+      <c r="I248" s="2" t="n"/>
+      <c r="J248" s="2" t="n"/>
+      <c r="K248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -13885,6 +15256,9 @@
       <c r="F249" s="2" t="n"/>
       <c r="G249" s="2" t="n"/>
       <c r="H249" s="2" t="n"/>
+      <c r="I249" s="2" t="n"/>
+      <c r="J249" s="2" t="n"/>
+      <c r="K249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -13895,6 +15269,9 @@
       <c r="F250" s="2" t="n"/>
       <c r="G250" s="2" t="n"/>
       <c r="H250" s="2" t="n"/>
+      <c r="I250" s="2" t="n"/>
+      <c r="J250" s="2" t="n"/>
+      <c r="K250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -13905,6 +15282,9 @@
       <c r="F251" s="2" t="n"/>
       <c r="G251" s="2" t="n"/>
       <c r="H251" s="2" t="n"/>
+      <c r="I251" s="2" t="n"/>
+      <c r="J251" s="2" t="n"/>
+      <c r="K251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -13915,6 +15295,9 @@
       <c r="F252" s="2" t="n"/>
       <c r="G252" s="2" t="n"/>
       <c r="H252" s="2" t="n"/>
+      <c r="I252" s="2" t="n"/>
+      <c r="J252" s="2" t="n"/>
+      <c r="K252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -13925,6 +15308,9 @@
       <c r="F253" s="2" t="n"/>
       <c r="G253" s="2" t="n"/>
       <c r="H253" s="2" t="n"/>
+      <c r="I253" s="2" t="n"/>
+      <c r="J253" s="2" t="n"/>
+      <c r="K253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -13935,6 +15321,9 @@
       <c r="F254" s="2" t="n"/>
       <c r="G254" s="2" t="n"/>
       <c r="H254" s="2" t="n"/>
+      <c r="I254" s="2" t="n"/>
+      <c r="J254" s="2" t="n"/>
+      <c r="K254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -13945,6 +15334,9 @@
       <c r="F255" s="2" t="n"/>
       <c r="G255" s="2" t="n"/>
       <c r="H255" s="2" t="n"/>
+      <c r="I255" s="2" t="n"/>
+      <c r="J255" s="2" t="n"/>
+      <c r="K255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -13955,6 +15347,9 @@
       <c r="F256" s="2" t="n"/>
       <c r="G256" s="2" t="n"/>
       <c r="H256" s="2" t="n"/>
+      <c r="I256" s="2" t="n"/>
+      <c r="J256" s="2" t="n"/>
+      <c r="K256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -13965,6 +15360,9 @@
       <c r="F257" s="2" t="n"/>
       <c r="G257" s="2" t="n"/>
       <c r="H257" s="2" t="n"/>
+      <c r="I257" s="2" t="n"/>
+      <c r="J257" s="2" t="n"/>
+      <c r="K257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -13975,6 +15373,9 @@
       <c r="F258" s="2" t="n"/>
       <c r="G258" s="2" t="n"/>
       <c r="H258" s="2" t="n"/>
+      <c r="I258" s="2" t="n"/>
+      <c r="J258" s="2" t="n"/>
+      <c r="K258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -13985,6 +15386,9 @@
       <c r="F259" s="2" t="n"/>
       <c r="G259" s="2" t="n"/>
       <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="n"/>
+      <c r="K259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -13995,6 +15399,9 @@
       <c r="F260" s="2" t="n"/>
       <c r="G260" s="2" t="n"/>
       <c r="H260" s="2" t="n"/>
+      <c r="I260" s="2" t="n"/>
+      <c r="J260" s="2" t="n"/>
+      <c r="K260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -14005,6 +15412,9 @@
       <c r="F261" s="2" t="n"/>
       <c r="G261" s="2" t="n"/>
       <c r="H261" s="2" t="n"/>
+      <c r="I261" s="2" t="n"/>
+      <c r="J261" s="2" t="n"/>
+      <c r="K261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -14015,6 +15425,9 @@
       <c r="F262" s="2" t="n"/>
       <c r="G262" s="2" t="n"/>
       <c r="H262" s="2" t="n"/>
+      <c r="I262" s="2" t="n"/>
+      <c r="J262" s="2" t="n"/>
+      <c r="K262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -14025,6 +15438,9 @@
       <c r="F263" s="2" t="n"/>
       <c r="G263" s="2" t="n"/>
       <c r="H263" s="2" t="n"/>
+      <c r="I263" s="2" t="n"/>
+      <c r="J263" s="2" t="n"/>
+      <c r="K263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -14035,6 +15451,9 @@
       <c r="F264" s="2" t="n"/>
       <c r="G264" s="2" t="n"/>
       <c r="H264" s="2" t="n"/>
+      <c r="I264" s="2" t="n"/>
+      <c r="J264" s="2" t="n"/>
+      <c r="K264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -14045,6 +15464,9 @@
       <c r="F265" s="2" t="n"/>
       <c r="G265" s="2" t="n"/>
       <c r="H265" s="2" t="n"/>
+      <c r="I265" s="2" t="n"/>
+      <c r="J265" s="2" t="n"/>
+      <c r="K265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -14055,6 +15477,9 @@
       <c r="F266" s="2" t="n"/>
       <c r="G266" s="2" t="n"/>
       <c r="H266" s="2" t="n"/>
+      <c r="I266" s="2" t="n"/>
+      <c r="J266" s="2" t="n"/>
+      <c r="K266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -14065,6 +15490,9 @@
       <c r="F267" s="2" t="n"/>
       <c r="G267" s="2" t="n"/>
       <c r="H267" s="2" t="n"/>
+      <c r="I267" s="2" t="n"/>
+      <c r="J267" s="2" t="n"/>
+      <c r="K267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -14075,6 +15503,9 @@
       <c r="F268" s="2" t="n"/>
       <c r="G268" s="2" t="n"/>
       <c r="H268" s="2" t="n"/>
+      <c r="I268" s="2" t="n"/>
+      <c r="J268" s="2" t="n"/>
+      <c r="K268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -14085,6 +15516,9 @@
       <c r="F269" s="2" t="n"/>
       <c r="G269" s="2" t="n"/>
       <c r="H269" s="2" t="n"/>
+      <c r="I269" s="2" t="n"/>
+      <c r="J269" s="2" t="n"/>
+      <c r="K269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -14095,6 +15529,9 @@
       <c r="F270" s="2" t="n"/>
       <c r="G270" s="2" t="n"/>
       <c r="H270" s="2" t="n"/>
+      <c r="I270" s="2" t="n"/>
+      <c r="J270" s="2" t="n"/>
+      <c r="K270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -14105,6 +15542,9 @@
       <c r="F271" s="2" t="n"/>
       <c r="G271" s="2" t="n"/>
       <c r="H271" s="2" t="n"/>
+      <c r="I271" s="2" t="n"/>
+      <c r="J271" s="2" t="n"/>
+      <c r="K271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -14115,6 +15555,9 @@
       <c r="F272" s="2" t="n"/>
       <c r="G272" s="2" t="n"/>
       <c r="H272" s="2" t="n"/>
+      <c r="I272" s="2" t="n"/>
+      <c r="J272" s="2" t="n"/>
+      <c r="K272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -14125,6 +15568,9 @@
       <c r="F273" s="2" t="n"/>
       <c r="G273" s="2" t="n"/>
       <c r="H273" s="2" t="n"/>
+      <c r="I273" s="2" t="n"/>
+      <c r="J273" s="2" t="n"/>
+      <c r="K273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -14135,6 +15581,9 @@
       <c r="F274" s="2" t="n"/>
       <c r="G274" s="2" t="n"/>
       <c r="H274" s="2" t="n"/>
+      <c r="I274" s="2" t="n"/>
+      <c r="J274" s="2" t="n"/>
+      <c r="K274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -14145,6 +15594,9 @@
       <c r="F275" s="2" t="n"/>
       <c r="G275" s="2" t="n"/>
       <c r="H275" s="2" t="n"/>
+      <c r="I275" s="2" t="n"/>
+      <c r="J275" s="2" t="n"/>
+      <c r="K275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -14155,6 +15607,9 @@
       <c r="F276" s="2" t="n"/>
       <c r="G276" s="2" t="n"/>
       <c r="H276" s="2" t="n"/>
+      <c r="I276" s="2" t="n"/>
+      <c r="J276" s="2" t="n"/>
+      <c r="K276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -14165,6 +15620,9 @@
       <c r="F277" s="2" t="n"/>
       <c r="G277" s="2" t="n"/>
       <c r="H277" s="2" t="n"/>
+      <c r="I277" s="2" t="n"/>
+      <c r="J277" s="2" t="n"/>
+      <c r="K277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -14175,6 +15633,9 @@
       <c r="F278" s="2" t="n"/>
       <c r="G278" s="2" t="n"/>
       <c r="H278" s="2" t="n"/>
+      <c r="I278" s="2" t="n"/>
+      <c r="J278" s="2" t="n"/>
+      <c r="K278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -14185,6 +15646,9 @@
       <c r="F279" s="2" t="n"/>
       <c r="G279" s="2" t="n"/>
       <c r="H279" s="2" t="n"/>
+      <c r="I279" s="2" t="n"/>
+      <c r="J279" s="2" t="n"/>
+      <c r="K279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -14195,6 +15659,9 @@
       <c r="F280" s="2" t="n"/>
       <c r="G280" s="2" t="n"/>
       <c r="H280" s="2" t="n"/>
+      <c r="I280" s="2" t="n"/>
+      <c r="J280" s="2" t="n"/>
+      <c r="K280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -14205,6 +15672,9 @@
       <c r="F281" s="2" t="n"/>
       <c r="G281" s="2" t="n"/>
       <c r="H281" s="2" t="n"/>
+      <c r="I281" s="2" t="n"/>
+      <c r="J281" s="2" t="n"/>
+      <c r="K281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -14215,6 +15685,9 @@
       <c r="F282" s="2" t="n"/>
       <c r="G282" s="2" t="n"/>
       <c r="H282" s="2" t="n"/>
+      <c r="I282" s="2" t="n"/>
+      <c r="J282" s="2" t="n"/>
+      <c r="K282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -14225,6 +15698,9 @@
       <c r="F283" s="2" t="n"/>
       <c r="G283" s="2" t="n"/>
       <c r="H283" s="2" t="n"/>
+      <c r="I283" s="2" t="n"/>
+      <c r="J283" s="2" t="n"/>
+      <c r="K283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -14235,6 +15711,9 @@
       <c r="F284" s="2" t="n"/>
       <c r="G284" s="2" t="n"/>
       <c r="H284" s="2" t="n"/>
+      <c r="I284" s="2" t="n"/>
+      <c r="J284" s="2" t="n"/>
+      <c r="K284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -14245,6 +15724,9 @@
       <c r="F285" s="2" t="n"/>
       <c r="G285" s="2" t="n"/>
       <c r="H285" s="2" t="n"/>
+      <c r="I285" s="2" t="n"/>
+      <c r="J285" s="2" t="n"/>
+      <c r="K285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -14255,6 +15737,9 @@
       <c r="F286" s="2" t="n"/>
       <c r="G286" s="2" t="n"/>
       <c r="H286" s="2" t="n"/>
+      <c r="I286" s="2" t="n"/>
+      <c r="J286" s="2" t="n"/>
+      <c r="K286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -14265,6 +15750,9 @@
       <c r="F287" s="2" t="n"/>
       <c r="G287" s="2" t="n"/>
       <c r="H287" s="2" t="n"/>
+      <c r="I287" s="2" t="n"/>
+      <c r="J287" s="2" t="n"/>
+      <c r="K287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -14275,6 +15763,9 @@
       <c r="F288" s="2" t="n"/>
       <c r="G288" s="2" t="n"/>
       <c r="H288" s="2" t="n"/>
+      <c r="I288" s="2" t="n"/>
+      <c r="J288" s="2" t="n"/>
+      <c r="K288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -14285,6 +15776,9 @@
       <c r="F289" s="2" t="n"/>
       <c r="G289" s="2" t="n"/>
       <c r="H289" s="2" t="n"/>
+      <c r="I289" s="2" t="n"/>
+      <c r="J289" s="2" t="n"/>
+      <c r="K289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -14295,6 +15789,9 @@
       <c r="F290" s="2" t="n"/>
       <c r="G290" s="2" t="n"/>
       <c r="H290" s="2" t="n"/>
+      <c r="I290" s="2" t="n"/>
+      <c r="J290" s="2" t="n"/>
+      <c r="K290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -14305,6 +15802,9 @@
       <c r="F291" s="2" t="n"/>
       <c r="G291" s="2" t="n"/>
       <c r="H291" s="2" t="n"/>
+      <c r="I291" s="2" t="n"/>
+      <c r="J291" s="2" t="n"/>
+      <c r="K291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -14315,6 +15815,9 @@
       <c r="F292" s="2" t="n"/>
       <c r="G292" s="2" t="n"/>
       <c r="H292" s="2" t="n"/>
+      <c r="I292" s="2" t="n"/>
+      <c r="J292" s="2" t="n"/>
+      <c r="K292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -14325,6 +15828,9 @@
       <c r="F293" s="2" t="n"/>
       <c r="G293" s="2" t="n"/>
       <c r="H293" s="2" t="n"/>
+      <c r="I293" s="2" t="n"/>
+      <c r="J293" s="2" t="n"/>
+      <c r="K293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -14335,6 +15841,9 @@
       <c r="F294" s="2" t="n"/>
       <c r="G294" s="2" t="n"/>
       <c r="H294" s="2" t="n"/>
+      <c r="I294" s="2" t="n"/>
+      <c r="J294" s="2" t="n"/>
+      <c r="K294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -14345,6 +15854,9 @@
       <c r="F295" s="2" t="n"/>
       <c r="G295" s="2" t="n"/>
       <c r="H295" s="2" t="n"/>
+      <c r="I295" s="2" t="n"/>
+      <c r="J295" s="2" t="n"/>
+      <c r="K295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -14355,6 +15867,9 @@
       <c r="F296" s="2" t="n"/>
       <c r="G296" s="2" t="n"/>
       <c r="H296" s="2" t="n"/>
+      <c r="I296" s="2" t="n"/>
+      <c r="J296" s="2" t="n"/>
+      <c r="K296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -14365,6 +15880,9 @@
       <c r="F297" s="2" t="n"/>
       <c r="G297" s="2" t="n"/>
       <c r="H297" s="2" t="n"/>
+      <c r="I297" s="2" t="n"/>
+      <c r="J297" s="2" t="n"/>
+      <c r="K297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -14375,6 +15893,9 @@
       <c r="F298" s="2" t="n"/>
       <c r="G298" s="2" t="n"/>
       <c r="H298" s="2" t="n"/>
+      <c r="I298" s="2" t="n"/>
+      <c r="J298" s="2" t="n"/>
+      <c r="K298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -14385,6 +15906,9 @@
       <c r="F299" s="2" t="n"/>
       <c r="G299" s="2" t="n"/>
       <c r="H299" s="2" t="n"/>
+      <c r="I299" s="2" t="n"/>
+      <c r="J299" s="2" t="n"/>
+      <c r="K299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -14395,6 +15919,9 @@
       <c r="F300" s="2" t="n"/>
       <c r="G300" s="2" t="n"/>
       <c r="H300" s="2" t="n"/>
+      <c r="I300" s="2" t="n"/>
+      <c r="J300" s="2" t="n"/>
+      <c r="K300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -14405,9 +15932,12 @@
       <c r="F301" s="2" t="n"/>
       <c r="G301" s="2" t="n"/>
       <c r="H301" s="2" t="n"/>
+      <c r="I301" s="2" t="n"/>
+      <c r="J301" s="2" t="n"/>
+      <c r="K301" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H301"/>
+  <autoFilter ref="A1:K301"/>
   <dataValidations count="2">
     <dataValidation sqref="C2:C301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="선택값 확인" error="목록의 값을 선택해주세요." type="list">
       <formula1>"주,부,혼합,부혼합"</formula1>

--- a/docs/intake-template.xlsx
+++ b/docs/intake-template.xlsx
@@ -842,17 +842,29 @@
       <c r="C43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>실적접수번호</t>
+        </is>
+      </c>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>실적신청번호</t>
+        </is>
+      </c>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>실적신청일</t>
+        </is>
+      </c>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
     </row>
